--- a/VerveStacks_FIN/vt_vervestacks_FIN_v1.xlsx
+++ b/VerveStacks_FIN/vt_vervestacks_FIN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D73E4794-1A97-4FDF-964A-88791C62D762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BDF5748-A9C4-421E-83A0-A48B40A07764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C4BED257-B859-448D-BA0A-62EB65DEB733}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A3E2AD59-B073-4A2E-869C-0195CC6814AC}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1382,7 +1382,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BBD210E-1AAB-4623-961F-FD142110CEE0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2540E49-0141-4EFE-A1E6-5961799647D1}">
   <dimension ref="B9:T53"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1461,19 +1461,19 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.133488</v>
+        <v>7.8154752000000022E-2</v>
       </c>
       <c r="F11">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G11">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H11">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I11">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J11" t="s">
         <v>38</v>
@@ -1517,19 +1517,19 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.133488</v>
+        <v>7.8154752000000022E-2</v>
       </c>
       <c r="F12">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G12">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H12">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I12">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J12" t="s">
         <v>39</v>
@@ -1573,19 +1573,19 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0.133488</v>
+        <v>7.8154752000000022E-2</v>
       </c>
       <c r="F13">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G13">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H13">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I13">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J13" t="s">
         <v>40</v>
@@ -1629,19 +1629,19 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.13765950000000002</v>
+        <v>8.0597088000000025E-2</v>
       </c>
       <c r="F14">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G14">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H14">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I14">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J14" t="s">
         <v>41</v>
@@ -1685,19 +1685,19 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.13765950000000002</v>
+        <v>8.0597088000000025E-2</v>
       </c>
       <c r="F15">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G15">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H15">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I15">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J15" t="s">
         <v>42</v>
@@ -1741,7 +1741,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.11272320000000002</v>
+        <v>8.7924096000000021E-2</v>
       </c>
       <c r="F16">
         <v>3583</v>
@@ -1797,19 +1797,19 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.30649709999999997</v>
+        <v>0.22872798</v>
       </c>
       <c r="F17">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G17">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H17">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I17">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J17" t="s">
         <v>43</v>
@@ -1853,7 +1853,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.38753750000000003</v>
+        <v>0.30227925</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -1909,7 +1909,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.34247500000000003</v>
+        <v>0.26713049999999999</v>
       </c>
       <c r="F19">
         <v>1365</v>
@@ -1965,7 +1965,7 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.450625</v>
+        <v>0.35148750000000001</v>
       </c>
       <c r="F20">
         <v>1365</v>
@@ -2021,7 +2021,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.46865000000000007</v>
+        <v>0.36554700000000012</v>
       </c>
       <c r="F21">
         <v>1365</v>
@@ -2077,7 +2077,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.450625</v>
+        <v>0.35148750000000006</v>
       </c>
       <c r="F22">
         <v>1365</v>
@@ -2133,7 +2133,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>0.47315625000000006</v>
+        <v>0.36906187500000009</v>
       </c>
       <c r="F23">
         <v>1365</v>
@@ -2189,7 +2189,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.50470000000000004</v>
+        <v>0.39366600000000013</v>
       </c>
       <c r="F24">
         <v>1365</v>
@@ -2245,7 +2245,7 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.54075000000000006</v>
+        <v>0.42178500000000008</v>
       </c>
       <c r="F25">
         <v>1365</v>
@@ -2301,7 +2301,7 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.21629999999999999</v>
+        <v>0.16871400000000006</v>
       </c>
       <c r="F26">
         <v>1365</v>
@@ -2357,7 +2357,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.21629999999999999</v>
+        <v>0.16871400000000006</v>
       </c>
       <c r="F27">
         <v>1365</v>
@@ -2413,7 +2413,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.23883125000000002</v>
+        <v>0.18628837500000006</v>
       </c>
       <c r="F28">
         <v>1365</v>
@@ -2469,7 +2469,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.30191875000000001</v>
+        <v>0.23549662500000007</v>
       </c>
       <c r="F29">
         <v>1365</v>
@@ -2525,7 +2525,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.48667500000000002</v>
+        <v>0.37960650000000007</v>
       </c>
       <c r="F30">
         <v>1365</v>
@@ -2581,7 +2581,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.19827500000000001</v>
+        <v>0.1546545</v>
       </c>
       <c r="F31">
         <v>1365</v>
@@ -2637,7 +2637,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.27037500000000003</v>
+        <v>0.21089250000000001</v>
       </c>
       <c r="F32">
         <v>1365</v>
@@ -2693,7 +2693,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.27037500000000003</v>
+        <v>0.21089250000000001</v>
       </c>
       <c r="F33">
         <v>1365</v>
@@ -2749,7 +2749,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.1892625</v>
+        <v>0.14762475</v>
       </c>
       <c r="F34">
         <v>1365</v>
@@ -2805,7 +2805,7 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>0.1892625</v>
+        <v>0.14762475</v>
       </c>
       <c r="F35">
         <v>1365</v>
@@ -2861,7 +2861,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>0.1892625</v>
+        <v>0.14762475</v>
       </c>
       <c r="F36">
         <v>1365</v>
@@ -2917,7 +2917,7 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>0.1892625</v>
+        <v>0.14762475</v>
       </c>
       <c r="F37">
         <v>1365</v>
@@ -2973,7 +2973,7 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>0.1892625</v>
+        <v>0.14762475</v>
       </c>
       <c r="F38">
         <v>1365</v>
@@ -3029,7 +3029,7 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>0.1892625</v>
+        <v>0.14762475</v>
       </c>
       <c r="F39">
         <v>1365</v>
@@ -3085,7 +3085,7 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>0.26136249999999994</v>
+        <v>0.20386274999999998</v>
       </c>
       <c r="F40">
         <v>1365</v>
@@ -3141,7 +3141,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>0.26136249999999994</v>
+        <v>0.20386274999999998</v>
       </c>
       <c r="F41">
         <v>1365</v>
@@ -3197,7 +3197,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>0.26136249999999994</v>
+        <v>0.20386274999999998</v>
       </c>
       <c r="F42">
         <v>1365</v>
@@ -3253,7 +3253,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>0.26136249999999994</v>
+        <v>0.20386274999999998</v>
       </c>
       <c r="F43">
         <v>1365</v>
@@ -3309,7 +3309,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.26136249999999994</v>
+        <v>0.20386274999999998</v>
       </c>
       <c r="F44">
         <v>1365</v>
@@ -3365,7 +3365,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.26136249999999994</v>
+        <v>0.20386274999999998</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -3421,7 +3421,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.26136249999999994</v>
+        <v>0.20386274999999998</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -3477,7 +3477,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.26136249999999994</v>
+        <v>0.20386274999999998</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -3533,7 +3533,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>0.26136249999999994</v>
+        <v>0.20386274999999998</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -3589,7 +3589,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>0.26136249999999994</v>
+        <v>0.20386274999999998</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -3645,7 +3645,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>0.26136249999999994</v>
+        <v>0.20386274999999998</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -3701,7 +3701,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>0.19827500000000001</v>
+        <v>0.1546545</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -3757,7 +3757,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>0.19827500000000001</v>
+        <v>0.1546545</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -3813,7 +3813,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>0.19827500000000001</v>
+        <v>0.1546545</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -3864,7 +3864,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F85DD83B-F12F-44CE-8DCF-E0644E060978}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{839A7AEC-B066-4385-976C-B329DB29FA75}">
   <dimension ref="B9:T132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3949,7 +3949,7 @@
         <v>0.03</v>
       </c>
       <c r="G11">
-        <v>0.28840000000000005</v>
+        <v>0.22495200000000004</v>
       </c>
       <c r="H11">
         <v>5197.5</v>
@@ -4002,7 +4002,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G12">
-        <v>0.28840000000000005</v>
+        <v>0.22495200000000004</v>
       </c>
       <c r="H12">
         <v>5197.5</v>
@@ -4055,7 +4055,7 @@
         <v>0.125</v>
       </c>
       <c r="G13">
-        <v>0.309</v>
+        <v>0.24101999999999998</v>
       </c>
       <c r="H13">
         <v>5197.5</v>
@@ -4108,7 +4108,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G14">
-        <v>0.309</v>
+        <v>0.24102000000000001</v>
       </c>
       <c r="H14">
         <v>5197.5</v>
@@ -4161,7 +4161,7 @@
         <v>4.7E-2</v>
       </c>
       <c r="G15">
-        <v>0.3296</v>
+        <v>0.25708800000000004</v>
       </c>
       <c r="H15">
         <v>5197.5</v>
@@ -4214,7 +4214,7 @@
         <v>1.0790000000000002</v>
       </c>
       <c r="G16">
-        <v>0.36049999999999999</v>
+        <v>0.28119</v>
       </c>
       <c r="H16">
         <v>3850.0000000000005</v>
@@ -4267,7 +4267,7 @@
         <v>0.26</v>
       </c>
       <c r="G17">
-        <v>0.31930000000000003</v>
+        <v>0.24905400000000003</v>
       </c>
       <c r="H17">
         <v>4427.5</v>
@@ -4320,7 +4320,7 @@
         <v>0.27</v>
       </c>
       <c r="G18">
-        <v>0.33990000000000004</v>
+        <v>0.26512200000000002</v>
       </c>
       <c r="H18">
         <v>4427.5</v>
@@ -4373,7 +4373,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="G19">
-        <v>0.25750000000000001</v>
+        <v>0.20084999999999997</v>
       </c>
       <c r="H19">
         <v>4427.5</v>
@@ -4426,7 +4426,7 @@
         <v>7.8E-2</v>
       </c>
       <c r="G20">
-        <v>0.31930000000000003</v>
+        <v>0.24905400000000005</v>
       </c>
       <c r="H20">
         <v>4427.5</v>
@@ -4479,7 +4479,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G21">
-        <v>0.31930000000000003</v>
+        <v>0.24905400000000003</v>
       </c>
       <c r="H21">
         <v>4427.5</v>
@@ -4532,7 +4532,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="G22">
-        <v>0.29869999999999997</v>
+        <v>0.232986</v>
       </c>
       <c r="H22">
         <v>4427.5</v>
@@ -4585,7 +4585,7 @@
         <v>0.05</v>
       </c>
       <c r="G23">
-        <v>0.309</v>
+        <v>0.24102000000000001</v>
       </c>
       <c r="H23">
         <v>5197.5</v>
@@ -4638,7 +4638,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G24">
-        <v>0.31930000000000003</v>
+        <v>0.24905400000000003</v>
       </c>
       <c r="H24">
         <v>4427.5</v>
@@ -4691,7 +4691,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="G25">
-        <v>0.31930000000000003</v>
+        <v>0.24905400000000005</v>
       </c>
       <c r="H25">
         <v>4427.5</v>
@@ -4744,7 +4744,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G26">
-        <v>0.27295000000000003</v>
+        <v>0.21290100000000003</v>
       </c>
       <c r="H26">
         <v>4427.5</v>
@@ -4797,7 +4797,7 @@
         <v>0.14199999999999999</v>
       </c>
       <c r="G27">
-        <v>0.31930000000000003</v>
+        <v>0.24905400000000005</v>
       </c>
       <c r="H27">
         <v>4427.5</v>
@@ -4850,7 +4850,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="G28">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H28">
         <v>4427.5</v>
@@ -4903,7 +4903,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="G29">
-        <v>0.26264999999999999</v>
+        <v>0.20486699999999999</v>
       </c>
       <c r="H29">
         <v>4427.5</v>
@@ -4956,7 +4956,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="G30">
-        <v>0.29869999999999997</v>
+        <v>0.232986</v>
       </c>
       <c r="H30">
         <v>4427.5</v>
@@ -5009,7 +5009,7 @@
         <v>0.107</v>
       </c>
       <c r="G31">
-        <v>0.31930000000000003</v>
+        <v>0.24905400000000003</v>
       </c>
       <c r="H31">
         <v>4427.5</v>
@@ -5062,7 +5062,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="G32">
-        <v>0.29869999999999997</v>
+        <v>0.232986</v>
       </c>
       <c r="H32">
         <v>4427.5</v>
@@ -5115,7 +5115,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="G33">
-        <v>0.26264999999999999</v>
+        <v>0.20486699999999999</v>
       </c>
       <c r="H33">
         <v>4427.5</v>
@@ -5168,7 +5168,7 @@
         <v>0.128</v>
       </c>
       <c r="G34">
-        <v>0.27295000000000003</v>
+        <v>0.21290100000000003</v>
       </c>
       <c r="H34">
         <v>4427.5</v>
@@ -5221,7 +5221,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="G35">
-        <v>0.31930000000000003</v>
+        <v>0.24905400000000003</v>
       </c>
       <c r="H35">
         <v>4427.5</v>
@@ -5274,7 +5274,7 @@
         <v>0.161</v>
       </c>
       <c r="G36">
-        <v>0.31930000000000003</v>
+        <v>0.24905400000000003</v>
       </c>
       <c r="H36">
         <v>4427.5</v>
@@ -5327,7 +5327,7 @@
         <v>0.30479999999999996</v>
       </c>
       <c r="G37">
-        <v>0.37080000000000002</v>
+        <v>0.28922400000000004</v>
       </c>
       <c r="H37">
         <v>2200</v>
@@ -5380,7 +5380,7 @@
         <v>3.9200000000000006E-2</v>
       </c>
       <c r="G38">
-        <v>0.3296</v>
+        <v>0.25708800000000004</v>
       </c>
       <c r="H38">
         <v>2970.0000000000005</v>
@@ -5433,7 +5433,7 @@
         <v>0.08</v>
       </c>
       <c r="G39">
-        <v>0.3296</v>
+        <v>0.25708800000000004</v>
       </c>
       <c r="H39">
         <v>2530</v>
@@ -5486,7 +5486,7 @@
         <v>0.125</v>
       </c>
       <c r="G40">
-        <v>0.3296</v>
+        <v>0.25708800000000004</v>
       </c>
       <c r="H40">
         <v>2530</v>
@@ -5539,7 +5539,7 @@
         <v>0.17699999999999999</v>
       </c>
       <c r="G41">
-        <v>0.33990000000000004</v>
+        <v>0.26512200000000002</v>
       </c>
       <c r="H41">
         <v>2530</v>
@@ -5592,7 +5592,7 @@
         <v>0.25</v>
       </c>
       <c r="G42">
-        <v>0.33990000000000004</v>
+        <v>0.26512200000000002</v>
       </c>
       <c r="H42">
         <v>2530</v>
@@ -5645,7 +5645,7 @@
         <v>0.61399999999999999</v>
       </c>
       <c r="G43">
-        <v>0.4017</v>
+        <v>0.31332599999999999</v>
       </c>
       <c r="H43">
         <v>2420</v>
@@ -5698,7 +5698,7 @@
         <v>0.60400000000000009</v>
       </c>
       <c r="G44">
-        <v>0.61799999999999999</v>
+        <v>0.48204000000000008</v>
       </c>
       <c r="H44">
         <v>1100</v>
@@ -5751,7 +5751,7 @@
         <v>0.14699999999999999</v>
       </c>
       <c r="G45">
-        <v>0.44290000000000002</v>
+        <v>0.34546200000000005</v>
       </c>
       <c r="H45">
         <v>1265</v>
@@ -5804,7 +5804,7 @@
         <v>0.129</v>
       </c>
       <c r="G46">
-        <v>0.39140000000000003</v>
+        <v>0.30529200000000001</v>
       </c>
       <c r="H46">
         <v>1265</v>
@@ -5857,7 +5857,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G47">
-        <v>0.51500000000000001</v>
+        <v>0.4017</v>
       </c>
       <c r="H47">
         <v>1265</v>
@@ -5910,7 +5910,7 @@
         <v>0.23400000000000001</v>
       </c>
       <c r="G48">
-        <v>0.53560000000000008</v>
+        <v>0.41776800000000014</v>
       </c>
       <c r="H48">
         <v>1265</v>
@@ -5963,7 +5963,7 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="G49">
-        <v>0.51500000000000001</v>
+        <v>0.40170000000000006</v>
       </c>
       <c r="H49">
         <v>1265</v>
@@ -6016,7 +6016,7 @@
         <v>0.48499999999999999</v>
       </c>
       <c r="G50">
-        <v>0.54075000000000006</v>
+        <v>0.42178500000000008</v>
       </c>
       <c r="H50">
         <v>1100</v>
@@ -6069,7 +6069,7 @@
         <v>0.125</v>
       </c>
       <c r="G51">
-        <v>0.57680000000000009</v>
+        <v>0.44990400000000014</v>
       </c>
       <c r="H51">
         <v>1265</v>
@@ -6122,7 +6122,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G52">
-        <v>0.2472</v>
+        <v>0.19281600000000004</v>
       </c>
       <c r="H52">
         <v>1188</v>
@@ -6175,7 +6175,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G53">
-        <v>0.2472</v>
+        <v>0.19281600000000004</v>
       </c>
       <c r="H53">
         <v>1188</v>
@@ -6228,7 +6228,7 @@
         <v>0.08</v>
       </c>
       <c r="G54">
-        <v>0.27295000000000003</v>
+        <v>0.21290100000000006</v>
       </c>
       <c r="H54">
         <v>1012</v>
@@ -6281,7 +6281,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="G55">
-        <v>0.34505000000000002</v>
+        <v>0.26913900000000007</v>
       </c>
       <c r="H55">
         <v>1782.0000000000002</v>
@@ -7712,7 +7712,7 @@
         <v>0.121</v>
       </c>
       <c r="G82">
-        <v>0.55620000000000003</v>
+        <v>0.43383600000000005</v>
       </c>
       <c r="H82">
         <v>1391.5</v>
@@ -7765,7 +7765,7 @@
         <v>0.10199999999999999</v>
       </c>
       <c r="G83">
-        <v>0.2266</v>
+        <v>0.17674800000000002</v>
       </c>
       <c r="H83">
         <v>1138.5</v>
@@ -7818,7 +7818,7 @@
         <v>0.16</v>
       </c>
       <c r="G84">
-        <v>0.309</v>
+        <v>0.24102000000000001</v>
       </c>
       <c r="H84">
         <v>1138.5</v>
@@ -7871,7 +7871,7 @@
         <v>0.16</v>
       </c>
       <c r="G85">
-        <v>0.309</v>
+        <v>0.24102000000000001</v>
       </c>
       <c r="H85">
         <v>1138.5</v>
@@ -7924,7 +7924,7 @@
         <v>0.03</v>
       </c>
       <c r="G86">
-        <v>0.21629999999999999</v>
+        <v>0.168714</v>
       </c>
       <c r="H86">
         <v>1336.5</v>
@@ -7977,7 +7977,7 @@
         <v>0.03</v>
       </c>
       <c r="G87">
-        <v>0.21629999999999999</v>
+        <v>0.168714</v>
       </c>
       <c r="H87">
         <v>1336.5</v>
@@ -8030,7 +8030,7 @@
         <v>0.03</v>
       </c>
       <c r="G88">
-        <v>0.21629999999999999</v>
+        <v>0.168714</v>
       </c>
       <c r="H88">
         <v>1336.5</v>
@@ -8083,7 +8083,7 @@
         <v>0.03</v>
       </c>
       <c r="G89">
-        <v>0.21629999999999999</v>
+        <v>0.168714</v>
       </c>
       <c r="H89">
         <v>1336.5</v>
@@ -8136,7 +8136,7 @@
         <v>0.03</v>
       </c>
       <c r="G90">
-        <v>0.21629999999999999</v>
+        <v>0.168714</v>
       </c>
       <c r="H90">
         <v>1336.5</v>
@@ -8189,7 +8189,7 @@
         <v>0.03</v>
       </c>
       <c r="G91">
-        <v>0.21629999999999999</v>
+        <v>0.168714</v>
       </c>
       <c r="H91">
         <v>1336.5</v>
@@ -8242,7 +8242,7 @@
         <v>0.03</v>
       </c>
       <c r="G92">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H92">
         <v>1336.5</v>
@@ -8295,7 +8295,7 @@
         <v>0.03</v>
       </c>
       <c r="G93">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H93">
         <v>1336.5</v>
@@ -8348,7 +8348,7 @@
         <v>0.02</v>
       </c>
       <c r="G94">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H94">
         <v>1336.5</v>
@@ -8401,7 +8401,7 @@
         <v>0.02</v>
       </c>
       <c r="G95">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H95">
         <v>1336.5</v>
@@ -8454,7 +8454,7 @@
         <v>0.05</v>
       </c>
       <c r="G96">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H96">
         <v>1336.5</v>
@@ -8507,7 +8507,7 @@
         <v>0.05</v>
       </c>
       <c r="G97">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H97">
         <v>1336.5</v>
@@ -8560,7 +8560,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G98">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H98">
         <v>1336.5</v>
@@ -8613,7 +8613,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G99">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H99">
         <v>1336.5</v>
@@ -8666,7 +8666,7 @@
         <v>0.02</v>
       </c>
       <c r="G100">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H100">
         <v>1336.5</v>
@@ -8719,7 +8719,7 @@
         <v>0.02</v>
       </c>
       <c r="G101">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H101">
         <v>1336.5</v>
@@ -8772,7 +8772,7 @@
         <v>0.05</v>
       </c>
       <c r="G102">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H102">
         <v>1336.5</v>
@@ -8825,7 +8825,7 @@
         <v>0.06</v>
       </c>
       <c r="G103">
-        <v>0.2266</v>
+        <v>0.17674800000000002</v>
       </c>
       <c r="H103">
         <v>1138.5</v>
@@ -8878,7 +8878,7 @@
         <v>0.06</v>
       </c>
       <c r="G104">
-        <v>0.2266</v>
+        <v>0.17674800000000002</v>
       </c>
       <c r="H104">
         <v>1138.5</v>
@@ -8931,7 +8931,7 @@
         <v>0.16200000000000001</v>
       </c>
       <c r="G105">
-        <v>0.22660000000000002</v>
+        <v>0.17674800000000002</v>
       </c>
       <c r="H105">
         <v>1138.5</v>

--- a/VerveStacks_FIN/vt_vervestacks_FIN_v1.xlsx
+++ b/VerveStacks_FIN/vt_vervestacks_FIN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BDF5748-A9C4-421E-83A0-A48B40A07764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{840D0473-8776-4324-A870-09942C6A86ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A3E2AD59-B073-4A2E-869C-0195CC6814AC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8C9DC727-5581-4F9D-9239-4BAF7BEA77BA}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1382,7 +1382,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2540E49-0141-4EFE-A1E6-5961799647D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3058A58-6604-4BF3-989F-CE0139161A52}">
   <dimension ref="B9:T53"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1461,7 +1461,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>7.8154752000000022E-2</v>
+        <v>7.9156736000000019E-2</v>
       </c>
       <c r="F11">
         <v>3583</v>
@@ -1517,7 +1517,7 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>7.8154752000000022E-2</v>
+        <v>7.9156736000000019E-2</v>
       </c>
       <c r="F12">
         <v>3583</v>
@@ -1573,7 +1573,7 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>7.8154752000000022E-2</v>
+        <v>7.9156736000000019E-2</v>
       </c>
       <c r="F13">
         <v>3583</v>
@@ -1629,7 +1629,7 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>8.0597088000000025E-2</v>
+        <v>8.1630384000000028E-2</v>
       </c>
       <c r="F14">
         <v>3583</v>
@@ -1685,7 +1685,7 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>8.0597088000000025E-2</v>
+        <v>8.1630384000000028E-2</v>
       </c>
       <c r="F15">
         <v>3583</v>
@@ -1741,7 +1741,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>8.7924096000000021E-2</v>
+        <v>8.9051328000000027E-2</v>
       </c>
       <c r="F16">
         <v>3583</v>
@@ -1797,7 +1797,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.22872798</v>
+        <v>0.23166039000000002</v>
       </c>
       <c r="F17">
         <v>2200</v>
@@ -1853,7 +1853,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.30227925</v>
+        <v>0.30615462500000001</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -1909,7 +1909,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.26713049999999999</v>
+        <v>0.27055525000000002</v>
       </c>
       <c r="F19">
         <v>1365</v>
@@ -1965,7 +1965,7 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.35148750000000001</v>
+        <v>0.35599375</v>
       </c>
       <c r="F20">
         <v>1365</v>
@@ -2021,7 +2021,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.36554700000000012</v>
+        <v>0.3702335000000001</v>
       </c>
       <c r="F21">
         <v>1365</v>
@@ -2077,7 +2077,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.35148750000000006</v>
+        <v>0.35599375</v>
       </c>
       <c r="F22">
         <v>1365</v>
@@ -2133,7 +2133,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>0.36906187500000009</v>
+        <v>0.3737934375000001</v>
       </c>
       <c r="F23">
         <v>1365</v>
@@ -2189,7 +2189,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.39366600000000013</v>
+        <v>0.39871300000000004</v>
       </c>
       <c r="F24">
         <v>1365</v>
@@ -2245,7 +2245,7 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.42178500000000008</v>
+        <v>0.42719250000000003</v>
       </c>
       <c r="F25">
         <v>1365</v>
@@ -2301,7 +2301,7 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.16871400000000006</v>
+        <v>0.17087699999999997</v>
       </c>
       <c r="F26">
         <v>1365</v>
@@ -2357,7 +2357,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.16871400000000006</v>
+        <v>0.17087699999999997</v>
       </c>
       <c r="F27">
         <v>1365</v>
@@ -2413,7 +2413,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.18628837500000006</v>
+        <v>0.1886766875</v>
       </c>
       <c r="F28">
         <v>1365</v>
@@ -2469,7 +2469,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.23549662500000007</v>
+        <v>0.23851581250000004</v>
       </c>
       <c r="F29">
         <v>1365</v>
@@ -2525,7 +2525,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.37960650000000007</v>
+        <v>0.38447325000000004</v>
       </c>
       <c r="F30">
         <v>1365</v>
@@ -2581,7 +2581,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.1546545</v>
+        <v>0.15663725000000001</v>
       </c>
       <c r="F31">
         <v>1365</v>
@@ -2637,7 +2637,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.21089250000000001</v>
+        <v>0.21359625000000002</v>
       </c>
       <c r="F32">
         <v>1365</v>
@@ -2693,7 +2693,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.21089250000000001</v>
+        <v>0.21359625000000002</v>
       </c>
       <c r="F33">
         <v>1365</v>
@@ -2749,7 +2749,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.14762475</v>
+        <v>0.14951737500000001</v>
       </c>
       <c r="F34">
         <v>1365</v>
@@ -2805,7 +2805,7 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>0.14762475</v>
+        <v>0.14951737500000001</v>
       </c>
       <c r="F35">
         <v>1365</v>
@@ -2861,7 +2861,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>0.14762475</v>
+        <v>0.14951737500000001</v>
       </c>
       <c r="F36">
         <v>1365</v>
@@ -2917,7 +2917,7 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>0.14762475</v>
+        <v>0.14951737500000001</v>
       </c>
       <c r="F37">
         <v>1365</v>
@@ -2973,7 +2973,7 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>0.14762475</v>
+        <v>0.14951737500000001</v>
       </c>
       <c r="F38">
         <v>1365</v>
@@ -3029,7 +3029,7 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>0.14762475</v>
+        <v>0.14951737500000001</v>
       </c>
       <c r="F39">
         <v>1365</v>
@@ -3085,7 +3085,7 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>0.20386274999999998</v>
+        <v>0.20647637499999999</v>
       </c>
       <c r="F40">
         <v>1365</v>
@@ -3141,7 +3141,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>0.20386274999999998</v>
+        <v>0.20647637499999999</v>
       </c>
       <c r="F41">
         <v>1365</v>
@@ -3197,7 +3197,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>0.20386274999999998</v>
+        <v>0.20647637499999999</v>
       </c>
       <c r="F42">
         <v>1365</v>
@@ -3253,7 +3253,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>0.20386274999999998</v>
+        <v>0.20647637499999999</v>
       </c>
       <c r="F43">
         <v>1365</v>
@@ -3309,7 +3309,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.20386274999999998</v>
+        <v>0.20647637499999999</v>
       </c>
       <c r="F44">
         <v>1365</v>
@@ -3365,7 +3365,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.20386274999999998</v>
+        <v>0.20647637499999999</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -3421,7 +3421,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.20386274999999998</v>
+        <v>0.20647637499999999</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -3477,7 +3477,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.20386274999999998</v>
+        <v>0.20647637499999999</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -3533,7 +3533,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>0.20386274999999998</v>
+        <v>0.20647637499999999</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -3589,7 +3589,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>0.20386274999999998</v>
+        <v>0.20647637499999999</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -3645,7 +3645,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>0.20386274999999998</v>
+        <v>0.20647637499999999</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -3701,7 +3701,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>0.1546545</v>
+        <v>0.15663725000000001</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -3757,7 +3757,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>0.1546545</v>
+        <v>0.15663725000000001</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -3813,7 +3813,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>0.1546545</v>
+        <v>0.15663725000000001</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -3864,7 +3864,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{839A7AEC-B066-4385-976C-B329DB29FA75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC1B1EFF-6151-414B-AFA3-F1D92F21A864}">
   <dimension ref="B9:T132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3949,7 +3949,7 @@
         <v>0.03</v>
       </c>
       <c r="G11">
-        <v>0.22495200000000004</v>
+        <v>0.22783600000000004</v>
       </c>
       <c r="H11">
         <v>5197.5</v>
@@ -4002,7 +4002,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G12">
-        <v>0.22495200000000004</v>
+        <v>0.22783600000000004</v>
       </c>
       <c r="H12">
         <v>5197.5</v>
@@ -4055,7 +4055,7 @@
         <v>0.125</v>
       </c>
       <c r="G13">
-        <v>0.24101999999999998</v>
+        <v>0.24411000000000002</v>
       </c>
       <c r="H13">
         <v>5197.5</v>
@@ -4108,7 +4108,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G14">
-        <v>0.24102000000000001</v>
+        <v>0.24411000000000002</v>
       </c>
       <c r="H14">
         <v>5197.5</v>
@@ -4161,7 +4161,7 @@
         <v>4.7E-2</v>
       </c>
       <c r="G15">
-        <v>0.25708800000000004</v>
+        <v>0.260384</v>
       </c>
       <c r="H15">
         <v>5197.5</v>
@@ -4214,7 +4214,7 @@
         <v>1.0790000000000002</v>
       </c>
       <c r="G16">
-        <v>0.28119</v>
+        <v>0.28479500000000002</v>
       </c>
       <c r="H16">
         <v>3850.0000000000005</v>
@@ -4267,7 +4267,7 @@
         <v>0.26</v>
       </c>
       <c r="G17">
-        <v>0.24905400000000003</v>
+        <v>0.25224700000000005</v>
       </c>
       <c r="H17">
         <v>4427.5</v>
@@ -4320,7 +4320,7 @@
         <v>0.27</v>
       </c>
       <c r="G18">
-        <v>0.26512200000000002</v>
+        <v>0.26852100000000007</v>
       </c>
       <c r="H18">
         <v>4427.5</v>
@@ -4373,7 +4373,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="G19">
-        <v>0.20084999999999997</v>
+        <v>0.20342500000000002</v>
       </c>
       <c r="H19">
         <v>4427.5</v>
@@ -4426,7 +4426,7 @@
         <v>7.8E-2</v>
       </c>
       <c r="G20">
-        <v>0.24905400000000005</v>
+        <v>0.25224700000000005</v>
       </c>
       <c r="H20">
         <v>4427.5</v>
@@ -4479,7 +4479,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G21">
-        <v>0.24905400000000003</v>
+        <v>0.25224700000000005</v>
       </c>
       <c r="H21">
         <v>4427.5</v>
@@ -4532,7 +4532,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="G22">
-        <v>0.232986</v>
+        <v>0.23597300000000002</v>
       </c>
       <c r="H22">
         <v>4427.5</v>
@@ -4585,7 +4585,7 @@
         <v>0.05</v>
       </c>
       <c r="G23">
-        <v>0.24102000000000001</v>
+        <v>0.24411000000000002</v>
       </c>
       <c r="H23">
         <v>5197.5</v>
@@ -4638,7 +4638,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G24">
-        <v>0.24905400000000003</v>
+        <v>0.25224700000000005</v>
       </c>
       <c r="H24">
         <v>4427.5</v>
@@ -4691,7 +4691,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="G25">
-        <v>0.24905400000000005</v>
+        <v>0.25224700000000005</v>
       </c>
       <c r="H25">
         <v>4427.5</v>
@@ -4744,7 +4744,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G26">
-        <v>0.21290100000000003</v>
+        <v>0.21563050000000003</v>
       </c>
       <c r="H26">
         <v>4427.5</v>
@@ -4797,7 +4797,7 @@
         <v>0.14199999999999999</v>
       </c>
       <c r="G27">
-        <v>0.24905400000000005</v>
+        <v>0.25224700000000005</v>
       </c>
       <c r="H27">
         <v>4427.5</v>
@@ -4850,7 +4850,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="G28">
-        <v>0.23298599999999997</v>
+        <v>0.23597300000000002</v>
       </c>
       <c r="H28">
         <v>4427.5</v>
@@ -4903,7 +4903,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="G29">
-        <v>0.20486699999999999</v>
+        <v>0.2074935</v>
       </c>
       <c r="H29">
         <v>4427.5</v>
@@ -4956,7 +4956,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="G30">
-        <v>0.232986</v>
+        <v>0.23597300000000002</v>
       </c>
       <c r="H30">
         <v>4427.5</v>
@@ -5009,7 +5009,7 @@
         <v>0.107</v>
       </c>
       <c r="G31">
-        <v>0.24905400000000003</v>
+        <v>0.25224700000000005</v>
       </c>
       <c r="H31">
         <v>4427.5</v>
@@ -5062,7 +5062,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="G32">
-        <v>0.232986</v>
+        <v>0.23597299999999996</v>
       </c>
       <c r="H32">
         <v>4427.5</v>
@@ -5115,7 +5115,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="G33">
-        <v>0.20486699999999999</v>
+        <v>0.2074935</v>
       </c>
       <c r="H33">
         <v>4427.5</v>
@@ -5168,7 +5168,7 @@
         <v>0.128</v>
       </c>
       <c r="G34">
-        <v>0.21290100000000003</v>
+        <v>0.21563050000000003</v>
       </c>
       <c r="H34">
         <v>4427.5</v>
@@ -5221,7 +5221,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="G35">
-        <v>0.24905400000000003</v>
+        <v>0.25224700000000005</v>
       </c>
       <c r="H35">
         <v>4427.5</v>
@@ -5274,7 +5274,7 @@
         <v>0.161</v>
       </c>
       <c r="G36">
-        <v>0.24905400000000003</v>
+        <v>0.25224700000000005</v>
       </c>
       <c r="H36">
         <v>4427.5</v>
@@ -5327,7 +5327,7 @@
         <v>0.30479999999999996</v>
       </c>
       <c r="G37">
-        <v>0.28922400000000004</v>
+        <v>0.29293200000000003</v>
       </c>
       <c r="H37">
         <v>2200</v>
@@ -5380,7 +5380,7 @@
         <v>3.9200000000000006E-2</v>
       </c>
       <c r="G38">
-        <v>0.25708800000000004</v>
+        <v>0.260384</v>
       </c>
       <c r="H38">
         <v>2970.0000000000005</v>
@@ -5433,7 +5433,7 @@
         <v>0.08</v>
       </c>
       <c r="G39">
-        <v>0.25708800000000004</v>
+        <v>0.260384</v>
       </c>
       <c r="H39">
         <v>2530</v>
@@ -5486,7 +5486,7 @@
         <v>0.125</v>
       </c>
       <c r="G40">
-        <v>0.25708800000000004</v>
+        <v>0.260384</v>
       </c>
       <c r="H40">
         <v>2530</v>
@@ -5539,7 +5539,7 @@
         <v>0.17699999999999999</v>
       </c>
       <c r="G41">
-        <v>0.26512200000000002</v>
+        <v>0.26852100000000007</v>
       </c>
       <c r="H41">
         <v>2530</v>
@@ -5592,7 +5592,7 @@
         <v>0.25</v>
       </c>
       <c r="G42">
-        <v>0.26512200000000002</v>
+        <v>0.26852100000000007</v>
       </c>
       <c r="H42">
         <v>2530</v>
@@ -5645,7 +5645,7 @@
         <v>0.61399999999999999</v>
       </c>
       <c r="G43">
-        <v>0.31332599999999999</v>
+        <v>0.31734300000000004</v>
       </c>
       <c r="H43">
         <v>2420</v>
@@ -5698,7 +5698,7 @@
         <v>0.60400000000000009</v>
       </c>
       <c r="G44">
-        <v>0.48204000000000008</v>
+        <v>0.48822000000000004</v>
       </c>
       <c r="H44">
         <v>1100</v>
@@ -5751,7 +5751,7 @@
         <v>0.14699999999999999</v>
       </c>
       <c r="G45">
-        <v>0.34546200000000005</v>
+        <v>0.34989100000000001</v>
       </c>
       <c r="H45">
         <v>1265</v>
@@ -5804,7 +5804,7 @@
         <v>0.129</v>
       </c>
       <c r="G46">
-        <v>0.30529200000000001</v>
+        <v>0.30920600000000004</v>
       </c>
       <c r="H46">
         <v>1265</v>
@@ -5857,7 +5857,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G47">
-        <v>0.4017</v>
+        <v>0.40685000000000004</v>
       </c>
       <c r="H47">
         <v>1265</v>
@@ -5910,7 +5910,7 @@
         <v>0.23400000000000001</v>
       </c>
       <c r="G48">
-        <v>0.41776800000000014</v>
+        <v>0.42312400000000006</v>
       </c>
       <c r="H48">
         <v>1265</v>
@@ -5963,7 +5963,7 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="G49">
-        <v>0.40170000000000006</v>
+        <v>0.40685000000000004</v>
       </c>
       <c r="H49">
         <v>1265</v>
@@ -6016,7 +6016,7 @@
         <v>0.48499999999999999</v>
       </c>
       <c r="G50">
-        <v>0.42178500000000008</v>
+        <v>0.42719250000000009</v>
       </c>
       <c r="H50">
         <v>1100</v>
@@ -6069,7 +6069,7 @@
         <v>0.125</v>
       </c>
       <c r="G51">
-        <v>0.44990400000000014</v>
+        <v>0.45567200000000008</v>
       </c>
       <c r="H51">
         <v>1265</v>
@@ -6122,7 +6122,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G52">
-        <v>0.19281600000000004</v>
+        <v>0.19528799999999999</v>
       </c>
       <c r="H52">
         <v>1188</v>
@@ -6175,7 +6175,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G53">
-        <v>0.19281600000000004</v>
+        <v>0.19528799999999999</v>
       </c>
       <c r="H53">
         <v>1188</v>
@@ -6228,7 +6228,7 @@
         <v>0.08</v>
       </c>
       <c r="G54">
-        <v>0.21290100000000006</v>
+        <v>0.2156305</v>
       </c>
       <c r="H54">
         <v>1012</v>
@@ -6281,7 +6281,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="G55">
-        <v>0.26913900000000007</v>
+        <v>0.27258950000000004</v>
       </c>
       <c r="H55">
         <v>1782.0000000000002</v>
@@ -7712,7 +7712,7 @@
         <v>0.121</v>
       </c>
       <c r="G82">
-        <v>0.43383600000000005</v>
+        <v>0.43939800000000007</v>
       </c>
       <c r="H82">
         <v>1391.5</v>
@@ -7765,7 +7765,7 @@
         <v>0.10199999999999999</v>
       </c>
       <c r="G83">
-        <v>0.17674800000000002</v>
+        <v>0.17901400000000001</v>
       </c>
       <c r="H83">
         <v>1138.5</v>
@@ -7818,7 +7818,7 @@
         <v>0.16</v>
       </c>
       <c r="G84">
-        <v>0.24102000000000001</v>
+        <v>0.24410999999999999</v>
       </c>
       <c r="H84">
         <v>1138.5</v>
@@ -7871,7 +7871,7 @@
         <v>0.16</v>
       </c>
       <c r="G85">
-        <v>0.24102000000000001</v>
+        <v>0.24410999999999999</v>
       </c>
       <c r="H85">
         <v>1138.5</v>
@@ -7924,7 +7924,7 @@
         <v>0.03</v>
       </c>
       <c r="G86">
-        <v>0.168714</v>
+        <v>0.170877</v>
       </c>
       <c r="H86">
         <v>1336.5</v>
@@ -7977,7 +7977,7 @@
         <v>0.03</v>
       </c>
       <c r="G87">
-        <v>0.168714</v>
+        <v>0.170877</v>
       </c>
       <c r="H87">
         <v>1336.5</v>
@@ -8030,7 +8030,7 @@
         <v>0.03</v>
       </c>
       <c r="G88">
-        <v>0.168714</v>
+        <v>0.170877</v>
       </c>
       <c r="H88">
         <v>1336.5</v>
@@ -8083,7 +8083,7 @@
         <v>0.03</v>
       </c>
       <c r="G89">
-        <v>0.168714</v>
+        <v>0.170877</v>
       </c>
       <c r="H89">
         <v>1336.5</v>
@@ -8136,7 +8136,7 @@
         <v>0.03</v>
       </c>
       <c r="G90">
-        <v>0.168714</v>
+        <v>0.170877</v>
       </c>
       <c r="H90">
         <v>1336.5</v>
@@ -8189,7 +8189,7 @@
         <v>0.03</v>
       </c>
       <c r="G91">
-        <v>0.168714</v>
+        <v>0.170877</v>
       </c>
       <c r="H91">
         <v>1336.5</v>
@@ -8242,7 +8242,7 @@
         <v>0.03</v>
       </c>
       <c r="G92">
-        <v>0.23298599999999997</v>
+        <v>0.23597299999999999</v>
       </c>
       <c r="H92">
         <v>1336.5</v>
@@ -8295,7 +8295,7 @@
         <v>0.03</v>
       </c>
       <c r="G93">
-        <v>0.23298599999999997</v>
+        <v>0.23597299999999999</v>
       </c>
       <c r="H93">
         <v>1336.5</v>
@@ -8348,7 +8348,7 @@
         <v>0.02</v>
       </c>
       <c r="G94">
-        <v>0.23298599999999997</v>
+        <v>0.23597299999999999</v>
       </c>
       <c r="H94">
         <v>1336.5</v>
@@ -8401,7 +8401,7 @@
         <v>0.02</v>
       </c>
       <c r="G95">
-        <v>0.23298599999999997</v>
+        <v>0.23597299999999999</v>
       </c>
       <c r="H95">
         <v>1336.5</v>
@@ -8454,7 +8454,7 @@
         <v>0.05</v>
       </c>
       <c r="G96">
-        <v>0.23298599999999997</v>
+        <v>0.23597299999999996</v>
       </c>
       <c r="H96">
         <v>1336.5</v>
@@ -8507,7 +8507,7 @@
         <v>0.05</v>
       </c>
       <c r="G97">
-        <v>0.23298599999999997</v>
+        <v>0.23597299999999996</v>
       </c>
       <c r="H97">
         <v>1336.5</v>
@@ -8560,7 +8560,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G98">
-        <v>0.23298599999999997</v>
+        <v>0.23597299999999999</v>
       </c>
       <c r="H98">
         <v>1336.5</v>
@@ -8613,7 +8613,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G99">
-        <v>0.23298599999999997</v>
+        <v>0.23597299999999999</v>
       </c>
       <c r="H99">
         <v>1336.5</v>
@@ -8666,7 +8666,7 @@
         <v>0.02</v>
       </c>
       <c r="G100">
-        <v>0.23298599999999997</v>
+        <v>0.23597299999999999</v>
       </c>
       <c r="H100">
         <v>1336.5</v>
@@ -8719,7 +8719,7 @@
         <v>0.02</v>
       </c>
       <c r="G101">
-        <v>0.23298599999999997</v>
+        <v>0.23597299999999999</v>
       </c>
       <c r="H101">
         <v>1336.5</v>
@@ -8772,7 +8772,7 @@
         <v>0.05</v>
       </c>
       <c r="G102">
-        <v>0.23298599999999997</v>
+        <v>0.23597299999999996</v>
       </c>
       <c r="H102">
         <v>1336.5</v>
@@ -8825,7 +8825,7 @@
         <v>0.06</v>
       </c>
       <c r="G103">
-        <v>0.17674800000000002</v>
+        <v>0.17901400000000001</v>
       </c>
       <c r="H103">
         <v>1138.5</v>
@@ -8878,7 +8878,7 @@
         <v>0.06</v>
       </c>
       <c r="G104">
-        <v>0.17674800000000002</v>
+        <v>0.17901400000000001</v>
       </c>
       <c r="H104">
         <v>1138.5</v>
@@ -8931,7 +8931,7 @@
         <v>0.16200000000000001</v>
       </c>
       <c r="G105">
-        <v>0.17674800000000002</v>
+        <v>0.17901400000000001</v>
       </c>
       <c r="H105">
         <v>1138.5</v>
